--- a/public/works/grid/pack-capacity-model-01.xlsx
+++ b/public/works/grid/pack-capacity-model-01.xlsx
@@ -170,7 +170,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0.####"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -180,12 +180,19 @@
     </font>
     <font>
       <b/>
+      <color rgb="FF153E2E"/>
       <sz val="14"/>
     </font>
     <font>
       <b/>
       <color rgb="FFFFFFFF"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <color rgb="FF24362E"/>
+    </font>
+    <font>
+      <color rgb="FF006D5B"/>
     </font>
   </fonts>
   <fills count="4">
@@ -202,7 +209,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F5F9"/>
+        <fgColor rgb="FFEDF5F0"/>
       </patternFill>
     </fill>
   </fills>
@@ -216,31 +223,31 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFB8C2CC"/>
+        <color rgb="FF828C88"/>
       </left>
       <right style="thin">
-        <color rgb="FFB8C2CC"/>
+        <color rgb="FF828C88"/>
       </right>
       <top style="thin">
-        <color rgb="FFB8C2CC"/>
+        <color rgb="FF828C88"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFB8C2CC"/>
+        <color rgb="FF828C88"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="hair">
-        <color rgb="FFD8DEE4"/>
+        <color rgb="FF828C88"/>
       </left>
       <right style="hair">
-        <color rgb="FFD8DEE4"/>
+        <color rgb="FF828C88"/>
       </right>
       <top style="hair">
-        <color rgb="FFD8DEE4"/>
+        <color rgb="FF828C88"/>
       </top>
       <bottom style="hair">
-        <color rgb="FFD8DEE4"/>
+        <color rgb="FF828C88"/>
       </bottom>
       <diagonal/>
     </border>
@@ -248,7 +255,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -258,10 +265,12 @@
     <xf numFmtId="164" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -775,15 +784,15 @@
       <c r="A11" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="B11" s="6">
+      <c r="B11" s="9">
         <f>B6*B7</f>
         <v>1200</v>
       </c>
-      <c r="C11" s="6">
+      <c r="C11" s="9">
         <f>C6*C7</f>
         <v>9600</v>
       </c>
-      <c r="D11" s="6">
+      <c r="D11" s="9">
         <f>D6*D7</f>
         <v>95200</v>
       </c>
@@ -795,15 +804,15 @@
       <c r="A12" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="B12" s="8">
+      <c r="B12" s="10">
         <f>B11*B5/1024</f>
         <v>21.1</v>
       </c>
-      <c r="C12" s="8">
+      <c r="C12" s="10">
         <f>C11*C5/1024</f>
         <v>225</v>
       </c>
-      <c r="D12" s="8">
+      <c r="D12" s="10">
         <f>D11*D5/1024</f>
         <v>3160.9</v>
       </c>
@@ -815,15 +824,15 @@
       <c r="A13" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="B13" s="6">
+      <c r="B13" s="9">
         <f>B12*B8</f>
         <v>2.5</v>
       </c>
-      <c r="C13" s="6">
+      <c r="C13" s="9">
         <f>C12*C8</f>
         <v>18</v>
       </c>
-      <c r="D13" s="6">
+      <c r="D13" s="9">
         <f>D12*D8</f>
         <v>158</v>
       </c>
@@ -835,15 +844,15 @@
       <c r="A14" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="B14" s="8">
+      <c r="B14" s="10">
         <f>B12+B13</f>
         <v>23.6</v>
       </c>
-      <c r="C14" s="8">
+      <c r="C14" s="10">
         <f>C12+C13</f>
         <v>243</v>
       </c>
-      <c r="D14" s="8">
+      <c r="D14" s="10">
         <f>D12+D13</f>
         <v>3319</v>
       </c>
@@ -855,15 +864,15 @@
       <c r="A15" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="B15" s="6">
+      <c r="B15" s="9">
         <f>B4-B14</f>
         <v>488.4</v>
       </c>
-      <c r="C15" s="6">
+      <c r="C15" s="9">
         <f>C4-C14</f>
         <v>1805</v>
       </c>
-      <c r="D15" s="6">
+      <c r="D15" s="9">
         <f>D4-D14</f>
         <v>4873</v>
       </c>
@@ -875,15 +884,15 @@
       <c r="A16" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="B16" s="8">
+      <c r="B16" s="10">
         <f>100*B11/119838</f>
         <v>1</v>
       </c>
-      <c r="C16" s="8">
+      <c r="C16" s="10">
         <f>100*C11/119838</f>
         <v>8.01</v>
       </c>
-      <c r="D16" s="8">
+      <c r="D16" s="10">
         <f>100*D11/119838</f>
         <v>79.44</v>
       </c>
@@ -895,15 +904,15 @@
       <c r="A17" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="B17" s="6">
+      <c r="B17" s="9">
         <f>100*B6/238</f>
         <v>12.61</v>
       </c>
-      <c r="C17" s="6">
+      <c r="C17" s="9">
         <f>100*C6/238</f>
         <v>33.61</v>
       </c>
-      <c r="D17" s="6">
+      <c r="D17" s="9">
         <f>100*D6/238</f>
         <v>100</v>
       </c>
@@ -915,15 +924,15 @@
       <c r="A18" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="B18" s="8">
+      <c r="B18" s="10">
         <f>1376.0</f>
         <v>1376</v>
       </c>
-      <c r="C18" s="8">
+      <c r="C18" s="10">
         <f>1376.0</f>
         <v>1376</v>
       </c>
-      <c r="D18" s="8">
+      <c r="D18" s="10">
         <f>1376.0</f>
         <v>1376</v>
       </c>
@@ -935,15 +944,15 @@
       <c r="A19" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B19" s="6">
+      <c r="B19" s="9">
         <f>B14+B18</f>
         <v>1399.6</v>
       </c>
-      <c r="C19" s="6">
+      <c r="C19" s="9">
         <f>C14+C18</f>
         <v>1619</v>
       </c>
-      <c r="D19" s="6">
+      <c r="D19" s="9">
         <f>D14+D18</f>
         <v>4695</v>
       </c>
@@ -989,15 +998,15 @@
       <c r="A22" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B22" s="8">
+      <c r="B22" s="10">
         <f>100*B14/B4</f>
         <v>4.61</v>
       </c>
-      <c r="C22" s="8">
+      <c r="C22" s="10">
         <f>100*C14/C4</f>
         <v>11.87</v>
       </c>
-      <c r="D22" s="8">
+      <c r="D22" s="10">
         <f>100*D14/D4</f>
         <v>40.51</v>
       </c>
@@ -1009,15 +1018,15 @@
       <c r="A23" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B23" s="6">
+      <c r="B23" s="9">
         <f>B14*1024/B11</f>
         <v>20.2</v>
       </c>
-      <c r="C23" s="6">
+      <c r="C23" s="9">
         <f>C14*1024/C11</f>
         <v>25.9</v>
       </c>
-      <c r="D23" s="6">
+      <c r="D23" s="9">
         <f>D14*1024/D11</f>
         <v>35.7</v>
       </c>
@@ -1029,15 +1038,15 @@
       <c r="A24" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="B24" s="8">
+      <c r="B24" s="10">
         <f>B15*1024/(B5*(1+B8))</f>
         <v>24806</v>
       </c>
-      <c r="C24" s="8">
+      <c r="C24" s="10">
         <f>C15*1024/(C5*(1+C8))</f>
         <v>71309</v>
       </c>
-      <c r="D24" s="8">
+      <c r="D24" s="10">
         <f>D15*1024/(D5*(1+D8))</f>
         <v>139775</v>
       </c>
@@ -1049,15 +1058,15 @@
       <c r="A25" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="B25" s="6">
+      <c r="B25" s="9">
         <f>100*B19/B4</f>
         <v>273.37</v>
       </c>
-      <c r="C25" s="6">
+      <c r="C25" s="9">
         <f>100*C19/C4</f>
         <v>79.05</v>
       </c>
-      <c r="D25" s="6">
+      <c r="D25" s="9">
         <f>100*D19/D4</f>
         <v>57.31</v>
       </c>
